--- a/src/main/resources/AllCollectionPages.xlsx
+++ b/src/main/resources/AllCollectionPages.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vijeta\git\TJAutomation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42CB670E-175A-4CE9-8A25-933386305B7B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59C0AE9-67DC-48A5-8E7B-CAAD50021D75}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{6E36BB93-8918-4A7C-A9DF-2D6DC4D87C0E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1</definedName>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t>URLs</t>
   </si>
@@ -81,9 +82,6 @@
     <t>https://tommyjohn.com/collections/mens-womens-underwear</t>
   </si>
   <si>
-    <t>https://tommyjohn.com/products/e-gift-card</t>
-  </si>
-  <si>
     <t>https://tommyjohn.com/collections/mens-underwear</t>
   </si>
   <si>
@@ -267,9 +265,6 @@
     <t>https://tommyjohn.com/pages/bras</t>
   </si>
   <si>
-    <t>https://tommyjohn.com/collections/womens-mix-and-match</t>
-  </si>
-  <si>
     <t>https://tommyjohn.com/collections/mens-pack</t>
   </si>
   <si>
@@ -322,6 +317,9 @@
   </si>
   <si>
     <t>https://tommyjohn.com/collections/womens-second-skin</t>
+  </si>
+  <si>
+    <t>https://staging.tommyjohn.com/collections/mens-trunk-1</t>
   </si>
 </sst>
 </file>
@@ -366,11 +364,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -686,7 +685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2C82410-DE23-46B1-9D53-2AA20A124B74}">
-  <dimension ref="A1:A96"/>
+  <dimension ref="A1:A95"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="98.54296875" bestFit="1" customWidth="1"/>
@@ -934,12 +933,12 @@
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.35">
@@ -959,7 +958,7 @@
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.35">
@@ -969,7 +968,7 @@
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.35">
@@ -1034,17 +1033,17 @@
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.35">
@@ -1069,7 +1068,7 @@
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.35">
@@ -1139,22 +1138,22 @@
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.35">
@@ -1163,17 +1162,11 @@
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A95" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A96" s="1" t="s">
-        <v>91</v>
+      <c r="A95" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A96" xr:uid="{36C3B95F-99B5-4B9D-BBC0-59F744D1099C}"/>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{A2753353-4518-44AA-884F-E2ADBA84D480}"/>
     <hyperlink ref="A3" r:id="rId2" xr:uid="{08302394-8AB6-4E03-AF2A-03DA2C3F0D6D}"/>
@@ -1189,86 +1182,97 @@
     <hyperlink ref="A13" r:id="rId12" xr:uid="{BB177064-29B6-45F8-AD78-B12E699A975B}"/>
     <hyperlink ref="A14" r:id="rId13" xr:uid="{6BB9EB4B-9F33-425B-8EC6-73F4CAAD161C}"/>
     <hyperlink ref="A15" r:id="rId14" xr:uid="{4838F18A-99B7-4DCD-B094-5AAF01F5A479}"/>
-    <hyperlink ref="A16" r:id="rId15" xr:uid="{DF38C03B-5D04-4B1C-8421-002E3F1816D2}"/>
-    <hyperlink ref="A17" r:id="rId16" xr:uid="{5A74722A-2914-4BBE-9480-09A477753682}"/>
-    <hyperlink ref="A18" r:id="rId17" xr:uid="{4172B904-8DD0-42FD-930A-BDF332FCBF74}"/>
-    <hyperlink ref="A19" r:id="rId18" xr:uid="{875414B1-72E3-42B9-9CF8-04E61E66630F}"/>
-    <hyperlink ref="A20" r:id="rId19" xr:uid="{E4F3706E-FB12-4F6A-B251-04A97FB5C587}"/>
-    <hyperlink ref="A21" r:id="rId20" xr:uid="{E2D8B15B-312F-4685-8FCE-EE49893D6042}"/>
-    <hyperlink ref="A22" r:id="rId21" xr:uid="{4D2BE94A-6917-4EBF-AF3E-C9CB4DFC35B1}"/>
-    <hyperlink ref="A23" r:id="rId22" xr:uid="{81D79FC2-AACB-489D-B3B9-3E9F03E7E4B9}"/>
-    <hyperlink ref="A24" r:id="rId23" xr:uid="{7601DEEA-FE82-4A84-AA2F-3B8041A6B5D6}"/>
-    <hyperlink ref="A25" r:id="rId24" xr:uid="{6060BBD1-6E78-48F4-8020-A0F279B035D3}"/>
-    <hyperlink ref="A26" r:id="rId25" xr:uid="{2BEA64D2-EEB6-46E9-82B4-60567942D191}"/>
-    <hyperlink ref="A27" r:id="rId26" xr:uid="{A9F1B6C6-5B63-46CF-B5BB-84CCDF4B7E78}"/>
-    <hyperlink ref="A28" r:id="rId27" xr:uid="{1D8BEAAF-C383-4C66-A878-2E11124598A7}"/>
-    <hyperlink ref="A29" r:id="rId28" xr:uid="{C4FA394D-EC01-4328-B935-B8CFF3B4DC57}"/>
-    <hyperlink ref="A30" r:id="rId29" xr:uid="{77075B89-8471-461C-AF45-BA40D762DC82}"/>
-    <hyperlink ref="A31" r:id="rId30" xr:uid="{50274DFF-09A2-49A0-8A8A-4E0DA74AE921}"/>
-    <hyperlink ref="A32" r:id="rId31" xr:uid="{DD5025BB-D8B7-4248-A4B4-467F2E8EE5B9}"/>
-    <hyperlink ref="A33" r:id="rId32" xr:uid="{B8033B37-0B9B-4675-8157-EAAFAA37FD12}"/>
-    <hyperlink ref="A34" r:id="rId33" xr:uid="{0DB9801B-569A-4358-9C58-B742EADA4561}"/>
-    <hyperlink ref="A35" r:id="rId34" xr:uid="{7CFD71CD-0A4D-4D3A-BC38-CD569CF77776}"/>
-    <hyperlink ref="A36" r:id="rId35" xr:uid="{949C40C2-E922-4D2C-9111-242B051177A5}"/>
-    <hyperlink ref="A37" r:id="rId36" xr:uid="{316AC240-04D3-4BA8-B5A0-C5FECF53BD97}"/>
-    <hyperlink ref="A38" r:id="rId37" xr:uid="{048CC2B8-F9C0-4F38-8EE6-0D30C061F46C}"/>
-    <hyperlink ref="A39" r:id="rId38" xr:uid="{3B104A6D-EBF4-4CDB-885B-808A720D7E49}"/>
-    <hyperlink ref="A40" r:id="rId39" xr:uid="{DA49711C-4AFC-4B29-9915-ED2A27B3AF33}"/>
-    <hyperlink ref="A41" r:id="rId40" xr:uid="{F885B5BA-DBEB-44C4-919B-CC22C99E1B7D}"/>
-    <hyperlink ref="A42" r:id="rId41" xr:uid="{3720BD22-1543-40B5-ABF3-C3AFFB4C222C}"/>
-    <hyperlink ref="A43" r:id="rId42" xr:uid="{A1167042-EE05-450E-B9D1-2FC46D0D8870}"/>
-    <hyperlink ref="A44" r:id="rId43" xr:uid="{526BBB12-7F38-4579-B263-6E7B821ED64B}"/>
-    <hyperlink ref="A45" r:id="rId44" xr:uid="{08991842-169D-4131-8E5C-0B23BF2231E4}"/>
-    <hyperlink ref="A46" r:id="rId45" xr:uid="{1980725C-6E8E-434A-BA30-7F025493AE0C}"/>
-    <hyperlink ref="A47" r:id="rId46" xr:uid="{A69D5B92-5F36-4F0D-8496-62C7779EF27C}"/>
-    <hyperlink ref="A48" r:id="rId47" xr:uid="{D58319EE-A17C-4704-B94D-03E499FA2F49}"/>
-    <hyperlink ref="A49" r:id="rId48" xr:uid="{920449F7-B769-4DA0-88C9-FC171552A0C2}"/>
-    <hyperlink ref="A51" r:id="rId49" xr:uid="{22DC2BD2-5ED5-453E-9772-4EBC80B76840}"/>
-    <hyperlink ref="A52" r:id="rId50" xr:uid="{B3016CBF-3B17-447C-8747-8883821F678C}"/>
-    <hyperlink ref="A53" r:id="rId51" xr:uid="{BCAD1D13-E879-487C-8991-BE4B5F26ED9D}"/>
-    <hyperlink ref="A54" r:id="rId52" xr:uid="{B24281AE-7CFB-4E77-8710-6C5C69DF0E3A}"/>
-    <hyperlink ref="A57" r:id="rId53" xr:uid="{9D345891-C64A-4116-9CBD-D8299A065AB2}"/>
-    <hyperlink ref="A58" r:id="rId54" xr:uid="{4A071EAE-97D2-4226-8320-18BD012FE980}"/>
-    <hyperlink ref="A59" r:id="rId55" xr:uid="{002D293B-E1E7-41D1-8F58-18CB033D4C0B}"/>
-    <hyperlink ref="A60" r:id="rId56" xr:uid="{CD479996-1364-46E4-8A92-9A6A42551FF6}"/>
-    <hyperlink ref="A61" r:id="rId57" xr:uid="{88C16AE5-2964-47DA-866E-C99E20C640BF}"/>
-    <hyperlink ref="A62" r:id="rId58" xr:uid="{DEE39071-BFD1-4659-BCBC-7253D2D83844}"/>
-    <hyperlink ref="A63" r:id="rId59" xr:uid="{124911A5-BF82-4A8A-90E3-3B307B75745A}"/>
-    <hyperlink ref="A64" r:id="rId60" xr:uid="{872676C7-BA93-44ED-8176-D65A522D055F}"/>
-    <hyperlink ref="A65" r:id="rId61" xr:uid="{8C69D9C5-F81F-43A4-88F1-F5072E510E74}"/>
-    <hyperlink ref="A66" r:id="rId62" xr:uid="{7AB8998F-8F34-45A4-B0AD-E6A7A0B2A881}"/>
-    <hyperlink ref="A67" r:id="rId63" xr:uid="{E59E2C03-FBE2-4EEE-AF2C-2EFBEABA12BE}"/>
-    <hyperlink ref="A68" r:id="rId64" xr:uid="{E98E434E-9191-4408-B92B-0C826578785E}"/>
-    <hyperlink ref="A69" r:id="rId65" xr:uid="{94690B43-F21E-4A61-B018-142AAE1B9ADB}"/>
-    <hyperlink ref="A72" r:id="rId66" xr:uid="{30179ED1-FF44-42C3-9D41-B7016703D894}"/>
-    <hyperlink ref="A73" r:id="rId67" xr:uid="{1ADF7731-1C78-48BE-AAA9-4C317A651BD8}"/>
-    <hyperlink ref="A74" r:id="rId68" xr:uid="{D2BC7663-6094-4414-9F29-42EB24D336C6}"/>
-    <hyperlink ref="A75" r:id="rId69" xr:uid="{2FFE24D8-5AB1-4F84-96BF-4128D22D12CC}"/>
-    <hyperlink ref="A76" r:id="rId70" xr:uid="{96A8D8B5-3A73-4548-814D-5DBC7029281A}"/>
-    <hyperlink ref="A55" r:id="rId71" xr:uid="{C95D41BC-2BE5-41DB-91BA-DDDADA812E67}"/>
-    <hyperlink ref="A77" r:id="rId72" xr:uid="{9C117DCB-567A-4238-B1DB-4E79F5FEFD0F}"/>
-    <hyperlink ref="A78" r:id="rId73" xr:uid="{39CDE5E9-80B4-431E-9B6A-23077E525A95}"/>
-    <hyperlink ref="A79" r:id="rId74" xr:uid="{851B6F22-EA97-4169-AFEA-1E55E7DAB8BB}"/>
-    <hyperlink ref="A80" r:id="rId75" xr:uid="{AD389BF8-D2FE-4E61-9AA3-4B70565D545D}"/>
-    <hyperlink ref="A81" r:id="rId76" xr:uid="{7211144F-07D8-4C74-998F-6DB44B3B9C9E}"/>
-    <hyperlink ref="A82" r:id="rId77" xr:uid="{269DB1EF-3835-4747-89A9-EF8F5B50AD58}"/>
-    <hyperlink ref="A83" r:id="rId78" xr:uid="{3A3D79C0-396E-45F0-9F95-323455383605}"/>
-    <hyperlink ref="A84" r:id="rId79" xr:uid="{7BD2167F-29F3-4974-8CCC-2A0B0452CDCB}"/>
-    <hyperlink ref="A85" r:id="rId80" xr:uid="{1E5B6BA8-A124-436E-B988-9A290CE1FF56}"/>
-    <hyperlink ref="A86" r:id="rId81" xr:uid="{8891F656-A5A3-4E45-B521-F203496DE824}"/>
-    <hyperlink ref="A87" r:id="rId82" xr:uid="{24F9B58E-0739-42CE-B33E-92641CD0D595}"/>
-    <hyperlink ref="A88" r:id="rId83" xr:uid="{C7443DD0-9344-40C4-874B-1767DBD50427}"/>
-    <hyperlink ref="A89" r:id="rId84" xr:uid="{AE4C65C3-8DCB-4AE5-8442-87A00ED8DCDB}"/>
-    <hyperlink ref="A90" r:id="rId85" xr:uid="{2CC71A87-9DD9-48D3-B3D0-197ABE68EDEE}"/>
-    <hyperlink ref="A91" r:id="rId86" xr:uid="{44AF49EA-475E-4A10-8D61-9C3C24AF667D}"/>
-    <hyperlink ref="A94" r:id="rId87" xr:uid="{1B9E0934-1E3E-44C6-ADF5-9D4FBE2966A9}"/>
-    <hyperlink ref="A95" r:id="rId88" xr:uid="{1512CE27-C7EE-4C2D-8EDC-C870908999A6}"/>
-    <hyperlink ref="A96" r:id="rId89" xr:uid="{4194F7AE-884A-4DC7-A28E-76CBEBD37199}"/>
-    <hyperlink ref="A93" r:id="rId90" xr:uid="{30AEC6DE-59B8-4F03-9BB0-94F9F7739D9A}"/>
-    <hyperlink ref="A56" r:id="rId91" xr:uid="{00567345-3DC5-4383-8379-17CFAA2A60F6}"/>
-    <hyperlink ref="A71" r:id="rId92" xr:uid="{23C81692-18EA-4785-AFF2-84B19A44313E}"/>
+    <hyperlink ref="A16" r:id="rId15" xr:uid="{5A74722A-2914-4BBE-9480-09A477753682}"/>
+    <hyperlink ref="A17" r:id="rId16" xr:uid="{4172B904-8DD0-42FD-930A-BDF332FCBF74}"/>
+    <hyperlink ref="A18" r:id="rId17" xr:uid="{875414B1-72E3-42B9-9CF8-04E61E66630F}"/>
+    <hyperlink ref="A19" r:id="rId18" xr:uid="{E4F3706E-FB12-4F6A-B251-04A97FB5C587}"/>
+    <hyperlink ref="A20" r:id="rId19" xr:uid="{E2D8B15B-312F-4685-8FCE-EE49893D6042}"/>
+    <hyperlink ref="A21" r:id="rId20" xr:uid="{4D2BE94A-6917-4EBF-AF3E-C9CB4DFC35B1}"/>
+    <hyperlink ref="A22" r:id="rId21" xr:uid="{81D79FC2-AACB-489D-B3B9-3E9F03E7E4B9}"/>
+    <hyperlink ref="A23" r:id="rId22" xr:uid="{7601DEEA-FE82-4A84-AA2F-3B8041A6B5D6}"/>
+    <hyperlink ref="A24" r:id="rId23" xr:uid="{6060BBD1-6E78-48F4-8020-A0F279B035D3}"/>
+    <hyperlink ref="A25" r:id="rId24" xr:uid="{2BEA64D2-EEB6-46E9-82B4-60567942D191}"/>
+    <hyperlink ref="A26" r:id="rId25" xr:uid="{A9F1B6C6-5B63-46CF-B5BB-84CCDF4B7E78}"/>
+    <hyperlink ref="A27" r:id="rId26" xr:uid="{1D8BEAAF-C383-4C66-A878-2E11124598A7}"/>
+    <hyperlink ref="A28" r:id="rId27" xr:uid="{C4FA394D-EC01-4328-B935-B8CFF3B4DC57}"/>
+    <hyperlink ref="A29" r:id="rId28" xr:uid="{77075B89-8471-461C-AF45-BA40D762DC82}"/>
+    <hyperlink ref="A30" r:id="rId29" xr:uid="{50274DFF-09A2-49A0-8A8A-4E0DA74AE921}"/>
+    <hyperlink ref="A31" r:id="rId30" xr:uid="{DD5025BB-D8B7-4248-A4B4-467F2E8EE5B9}"/>
+    <hyperlink ref="A32" r:id="rId31" xr:uid="{B8033B37-0B9B-4675-8157-EAAFAA37FD12}"/>
+    <hyperlink ref="A33" r:id="rId32" xr:uid="{0DB9801B-569A-4358-9C58-B742EADA4561}"/>
+    <hyperlink ref="A34" r:id="rId33" xr:uid="{7CFD71CD-0A4D-4D3A-BC38-CD569CF77776}"/>
+    <hyperlink ref="A35" r:id="rId34" xr:uid="{949C40C2-E922-4D2C-9111-242B051177A5}"/>
+    <hyperlink ref="A36" r:id="rId35" xr:uid="{316AC240-04D3-4BA8-B5A0-C5FECF53BD97}"/>
+    <hyperlink ref="A37" r:id="rId36" xr:uid="{048CC2B8-F9C0-4F38-8EE6-0D30C061F46C}"/>
+    <hyperlink ref="A38" r:id="rId37" xr:uid="{3B104A6D-EBF4-4CDB-885B-808A720D7E49}"/>
+    <hyperlink ref="A39" r:id="rId38" xr:uid="{DA49711C-4AFC-4B29-9915-ED2A27B3AF33}"/>
+    <hyperlink ref="A40" r:id="rId39" xr:uid="{F885B5BA-DBEB-44C4-919B-CC22C99E1B7D}"/>
+    <hyperlink ref="A41" r:id="rId40" xr:uid="{3720BD22-1543-40B5-ABF3-C3AFFB4C222C}"/>
+    <hyperlink ref="A42" r:id="rId41" xr:uid="{A1167042-EE05-450E-B9D1-2FC46D0D8870}"/>
+    <hyperlink ref="A43" r:id="rId42" xr:uid="{526BBB12-7F38-4579-B263-6E7B821ED64B}"/>
+    <hyperlink ref="A44" r:id="rId43" xr:uid="{08991842-169D-4131-8E5C-0B23BF2231E4}"/>
+    <hyperlink ref="A45" r:id="rId44" xr:uid="{1980725C-6E8E-434A-BA30-7F025493AE0C}"/>
+    <hyperlink ref="A46" r:id="rId45" xr:uid="{A69D5B92-5F36-4F0D-8496-62C7779EF27C}"/>
+    <hyperlink ref="A47" r:id="rId46" xr:uid="{D58319EE-A17C-4704-B94D-03E499FA2F49}"/>
+    <hyperlink ref="A48" r:id="rId47" xr:uid="{920449F7-B769-4DA0-88C9-FC171552A0C2}"/>
+    <hyperlink ref="A50" r:id="rId48" xr:uid="{22DC2BD2-5ED5-453E-9772-4EBC80B76840}"/>
+    <hyperlink ref="A51" r:id="rId49" xr:uid="{B3016CBF-3B17-447C-8747-8883821F678C}"/>
+    <hyperlink ref="A52" r:id="rId50" xr:uid="{BCAD1D13-E879-487C-8991-BE4B5F26ED9D}"/>
+    <hyperlink ref="A53" r:id="rId51" xr:uid="{B24281AE-7CFB-4E77-8710-6C5C69DF0E3A}"/>
+    <hyperlink ref="A56" r:id="rId52" xr:uid="{9D345891-C64A-4116-9CBD-D8299A065AB2}"/>
+    <hyperlink ref="A57" r:id="rId53" xr:uid="{4A071EAE-97D2-4226-8320-18BD012FE980}"/>
+    <hyperlink ref="A58" r:id="rId54" xr:uid="{002D293B-E1E7-41D1-8F58-18CB033D4C0B}"/>
+    <hyperlink ref="A59" r:id="rId55" xr:uid="{CD479996-1364-46E4-8A92-9A6A42551FF6}"/>
+    <hyperlink ref="A60" r:id="rId56" xr:uid="{88C16AE5-2964-47DA-866E-C99E20C640BF}"/>
+    <hyperlink ref="A61" r:id="rId57" xr:uid="{DEE39071-BFD1-4659-BCBC-7253D2D83844}"/>
+    <hyperlink ref="A62" r:id="rId58" xr:uid="{124911A5-BF82-4A8A-90E3-3B307B75745A}"/>
+    <hyperlink ref="A63" r:id="rId59" xr:uid="{872676C7-BA93-44ED-8176-D65A522D055F}"/>
+    <hyperlink ref="A64" r:id="rId60" xr:uid="{8C69D9C5-F81F-43A4-88F1-F5072E510E74}"/>
+    <hyperlink ref="A65" r:id="rId61" xr:uid="{7AB8998F-8F34-45A4-B0AD-E6A7A0B2A881}"/>
+    <hyperlink ref="A66" r:id="rId62" xr:uid="{E59E2C03-FBE2-4EEE-AF2C-2EFBEABA12BE}"/>
+    <hyperlink ref="A67" r:id="rId63" xr:uid="{E98E434E-9191-4408-B92B-0C826578785E}"/>
+    <hyperlink ref="A68" r:id="rId64" xr:uid="{94690B43-F21E-4A61-B018-142AAE1B9ADB}"/>
+    <hyperlink ref="A71" r:id="rId65" xr:uid="{30179ED1-FF44-42C3-9D41-B7016703D894}"/>
+    <hyperlink ref="A72" r:id="rId66" xr:uid="{1ADF7731-1C78-48BE-AAA9-4C317A651BD8}"/>
+    <hyperlink ref="A73" r:id="rId67" xr:uid="{D2BC7663-6094-4414-9F29-42EB24D336C6}"/>
+    <hyperlink ref="A74" r:id="rId68" xr:uid="{2FFE24D8-5AB1-4F84-96BF-4128D22D12CC}"/>
+    <hyperlink ref="A75" r:id="rId69" xr:uid="{96A8D8B5-3A73-4548-814D-5DBC7029281A}"/>
+    <hyperlink ref="A54" r:id="rId70" xr:uid="{C95D41BC-2BE5-41DB-91BA-DDDADA812E67}"/>
+    <hyperlink ref="A76" r:id="rId71" xr:uid="{9C117DCB-567A-4238-B1DB-4E79F5FEFD0F}"/>
+    <hyperlink ref="A77" r:id="rId72" xr:uid="{39CDE5E9-80B4-431E-9B6A-23077E525A95}"/>
+    <hyperlink ref="A78" r:id="rId73" xr:uid="{851B6F22-EA97-4169-AFEA-1E55E7DAB8BB}"/>
+    <hyperlink ref="A79" r:id="rId74" xr:uid="{7211144F-07D8-4C74-998F-6DB44B3B9C9E}"/>
+    <hyperlink ref="A80" r:id="rId75" xr:uid="{269DB1EF-3835-4747-89A9-EF8F5B50AD58}"/>
+    <hyperlink ref="A81" r:id="rId76" xr:uid="{3A3D79C0-396E-45F0-9F95-323455383605}"/>
+    <hyperlink ref="A82" r:id="rId77" xr:uid="{7BD2167F-29F3-4974-8CCC-2A0B0452CDCB}"/>
+    <hyperlink ref="A83" r:id="rId78" xr:uid="{1E5B6BA8-A124-436E-B988-9A290CE1FF56}"/>
+    <hyperlink ref="A84" r:id="rId79" xr:uid="{8891F656-A5A3-4E45-B521-F203496DE824}"/>
+    <hyperlink ref="A85" r:id="rId80" xr:uid="{24F9B58E-0739-42CE-B33E-92641CD0D595}"/>
+    <hyperlink ref="A86" r:id="rId81" xr:uid="{C7443DD0-9344-40C4-874B-1767DBD50427}"/>
+    <hyperlink ref="A87" r:id="rId82" xr:uid="{AE4C65C3-8DCB-4AE5-8442-87A00ED8DCDB}"/>
+    <hyperlink ref="A88" r:id="rId83" xr:uid="{2CC71A87-9DD9-48D3-B3D0-197ABE68EDEE}"/>
+    <hyperlink ref="A89" r:id="rId84" xr:uid="{44AF49EA-475E-4A10-8D61-9C3C24AF667D}"/>
+    <hyperlink ref="A92" r:id="rId85" xr:uid="{1B9E0934-1E3E-44C6-ADF5-9D4FBE2966A9}"/>
+    <hyperlink ref="A93" r:id="rId86" xr:uid="{1512CE27-C7EE-4C2D-8EDC-C870908999A6}"/>
+    <hyperlink ref="A94" r:id="rId87" xr:uid="{4194F7AE-884A-4DC7-A28E-76CBEBD37199}"/>
+    <hyperlink ref="A91" r:id="rId88" xr:uid="{30AEC6DE-59B8-4F03-9BB0-94F9F7739D9A}"/>
+    <hyperlink ref="A55" r:id="rId89" xr:uid="{00567345-3DC5-4383-8379-17CFAA2A60F6}"/>
+    <hyperlink ref="A70" r:id="rId90" xr:uid="{23C81692-18EA-4785-AFF2-84B19A44313E}"/>
+    <hyperlink ref="A95" r:id="rId91" xr:uid="{1C10C088-FB94-4305-819C-108DF970BDB8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId93"/>
+  <pageSetup orientation="portrait" r:id="rId92"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0A92C8C-C1EC-48C2-A6C1-E0CB36E8F620}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="98.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/main/resources/AllCollectionPages.xlsx
+++ b/src/main/resources/AllCollectionPages.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vijeta\git\TJAutomation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59C0AE9-67DC-48A5-8E7B-CAAD50021D75}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87C6438C-FE36-47A2-8454-D476AD198BF0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{6E36BB93-8918-4A7C-A9DF-2D6DC4D87C0E}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t>URLs</t>
   </si>
@@ -317,9 +317,6 @@
   </si>
   <si>
     <t>https://tommyjohn.com/collections/womens-second-skin</t>
-  </si>
-  <si>
-    <t>https://staging.tommyjohn.com/collections/mens-trunk-1</t>
   </si>
 </sst>
 </file>
@@ -1162,9 +1159,7 @@
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A95" s="2" t="s">
-        <v>94</v>
-      </c>
+      <c r="A95" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1258,10 +1253,9 @@
     <hyperlink ref="A91" r:id="rId88" xr:uid="{30AEC6DE-59B8-4F03-9BB0-94F9F7739D9A}"/>
     <hyperlink ref="A55" r:id="rId89" xr:uid="{00567345-3DC5-4383-8379-17CFAA2A60F6}"/>
     <hyperlink ref="A70" r:id="rId90" xr:uid="{23C81692-18EA-4785-AFF2-84B19A44313E}"/>
-    <hyperlink ref="A95" r:id="rId91" xr:uid="{1C10C088-FB94-4305-819C-108DF970BDB8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId92"/>
+  <pageSetup orientation="portrait" r:id="rId91"/>
 </worksheet>
 </file>
 

--- a/src/main/resources/AllCollectionPages.xlsx
+++ b/src/main/resources/AllCollectionPages.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vijeta\git\TJAutomation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87C6438C-FE36-47A2-8454-D476AD198BF0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC0805B-EA09-49AF-9F48-F0728FB9CBB4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{6E36BB93-8918-4A7C-A9DF-2D6DC4D87C0E}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
   <si>
     <t>URLs</t>
   </si>
@@ -158,9 +158,6 @@
   </si>
   <si>
     <t>https://tommyjohn.com/pages/mens-shop-the-look</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/all-mens-collections</t>
   </si>
   <si>
     <t>https://tommyjohn.com/collections/mens-second-skin</t>
@@ -682,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2C82410-DE23-46B1-9D53-2AA20A124B74}">
-  <dimension ref="A1:A95"/>
+  <dimension ref="A1:A94"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="98.54296875" bestFit="1" customWidth="1"/>
@@ -925,12 +922,12 @@
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.35">
@@ -950,7 +947,7 @@
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.35">
@@ -960,7 +957,7 @@
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.35">
@@ -1025,17 +1022,17 @@
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.35">
@@ -1060,7 +1057,7 @@
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.35">
@@ -1130,17 +1127,17 @@
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.35">
@@ -1154,12 +1151,7 @@
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A94" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A95" s="2"/>
+      <c r="A94" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1203,59 +1195,58 @@
     <hyperlink ref="A39" r:id="rId38" xr:uid="{DA49711C-4AFC-4B29-9915-ED2A27B3AF33}"/>
     <hyperlink ref="A40" r:id="rId39" xr:uid="{F885B5BA-DBEB-44C4-919B-CC22C99E1B7D}"/>
     <hyperlink ref="A41" r:id="rId40" xr:uid="{3720BD22-1543-40B5-ABF3-C3AFFB4C222C}"/>
-    <hyperlink ref="A42" r:id="rId41" xr:uid="{A1167042-EE05-450E-B9D1-2FC46D0D8870}"/>
-    <hyperlink ref="A43" r:id="rId42" xr:uid="{526BBB12-7F38-4579-B263-6E7B821ED64B}"/>
-    <hyperlink ref="A44" r:id="rId43" xr:uid="{08991842-169D-4131-8E5C-0B23BF2231E4}"/>
-    <hyperlink ref="A45" r:id="rId44" xr:uid="{1980725C-6E8E-434A-BA30-7F025493AE0C}"/>
-    <hyperlink ref="A46" r:id="rId45" xr:uid="{A69D5B92-5F36-4F0D-8496-62C7779EF27C}"/>
-    <hyperlink ref="A47" r:id="rId46" xr:uid="{D58319EE-A17C-4704-B94D-03E499FA2F49}"/>
-    <hyperlink ref="A48" r:id="rId47" xr:uid="{920449F7-B769-4DA0-88C9-FC171552A0C2}"/>
-    <hyperlink ref="A50" r:id="rId48" xr:uid="{22DC2BD2-5ED5-453E-9772-4EBC80B76840}"/>
-    <hyperlink ref="A51" r:id="rId49" xr:uid="{B3016CBF-3B17-447C-8747-8883821F678C}"/>
-    <hyperlink ref="A52" r:id="rId50" xr:uid="{BCAD1D13-E879-487C-8991-BE4B5F26ED9D}"/>
-    <hyperlink ref="A53" r:id="rId51" xr:uid="{B24281AE-7CFB-4E77-8710-6C5C69DF0E3A}"/>
-    <hyperlink ref="A56" r:id="rId52" xr:uid="{9D345891-C64A-4116-9CBD-D8299A065AB2}"/>
-    <hyperlink ref="A57" r:id="rId53" xr:uid="{4A071EAE-97D2-4226-8320-18BD012FE980}"/>
-    <hyperlink ref="A58" r:id="rId54" xr:uid="{002D293B-E1E7-41D1-8F58-18CB033D4C0B}"/>
-    <hyperlink ref="A59" r:id="rId55" xr:uid="{CD479996-1364-46E4-8A92-9A6A42551FF6}"/>
-    <hyperlink ref="A60" r:id="rId56" xr:uid="{88C16AE5-2964-47DA-866E-C99E20C640BF}"/>
-    <hyperlink ref="A61" r:id="rId57" xr:uid="{DEE39071-BFD1-4659-BCBC-7253D2D83844}"/>
-    <hyperlink ref="A62" r:id="rId58" xr:uid="{124911A5-BF82-4A8A-90E3-3B307B75745A}"/>
-    <hyperlink ref="A63" r:id="rId59" xr:uid="{872676C7-BA93-44ED-8176-D65A522D055F}"/>
-    <hyperlink ref="A64" r:id="rId60" xr:uid="{8C69D9C5-F81F-43A4-88F1-F5072E510E74}"/>
-    <hyperlink ref="A65" r:id="rId61" xr:uid="{7AB8998F-8F34-45A4-B0AD-E6A7A0B2A881}"/>
-    <hyperlink ref="A66" r:id="rId62" xr:uid="{E59E2C03-FBE2-4EEE-AF2C-2EFBEABA12BE}"/>
-    <hyperlink ref="A67" r:id="rId63" xr:uid="{E98E434E-9191-4408-B92B-0C826578785E}"/>
-    <hyperlink ref="A68" r:id="rId64" xr:uid="{94690B43-F21E-4A61-B018-142AAE1B9ADB}"/>
-    <hyperlink ref="A71" r:id="rId65" xr:uid="{30179ED1-FF44-42C3-9D41-B7016703D894}"/>
-    <hyperlink ref="A72" r:id="rId66" xr:uid="{1ADF7731-1C78-48BE-AAA9-4C317A651BD8}"/>
-    <hyperlink ref="A73" r:id="rId67" xr:uid="{D2BC7663-6094-4414-9F29-42EB24D336C6}"/>
-    <hyperlink ref="A74" r:id="rId68" xr:uid="{2FFE24D8-5AB1-4F84-96BF-4128D22D12CC}"/>
-    <hyperlink ref="A75" r:id="rId69" xr:uid="{96A8D8B5-3A73-4548-814D-5DBC7029281A}"/>
-    <hyperlink ref="A54" r:id="rId70" xr:uid="{C95D41BC-2BE5-41DB-91BA-DDDADA812E67}"/>
-    <hyperlink ref="A76" r:id="rId71" xr:uid="{9C117DCB-567A-4238-B1DB-4E79F5FEFD0F}"/>
-    <hyperlink ref="A77" r:id="rId72" xr:uid="{39CDE5E9-80B4-431E-9B6A-23077E525A95}"/>
-    <hyperlink ref="A78" r:id="rId73" xr:uid="{851B6F22-EA97-4169-AFEA-1E55E7DAB8BB}"/>
-    <hyperlink ref="A79" r:id="rId74" xr:uid="{7211144F-07D8-4C74-998F-6DB44B3B9C9E}"/>
-    <hyperlink ref="A80" r:id="rId75" xr:uid="{269DB1EF-3835-4747-89A9-EF8F5B50AD58}"/>
-    <hyperlink ref="A81" r:id="rId76" xr:uid="{3A3D79C0-396E-45F0-9F95-323455383605}"/>
-    <hyperlink ref="A82" r:id="rId77" xr:uid="{7BD2167F-29F3-4974-8CCC-2A0B0452CDCB}"/>
-    <hyperlink ref="A83" r:id="rId78" xr:uid="{1E5B6BA8-A124-436E-B988-9A290CE1FF56}"/>
-    <hyperlink ref="A84" r:id="rId79" xr:uid="{8891F656-A5A3-4E45-B521-F203496DE824}"/>
-    <hyperlink ref="A85" r:id="rId80" xr:uid="{24F9B58E-0739-42CE-B33E-92641CD0D595}"/>
-    <hyperlink ref="A86" r:id="rId81" xr:uid="{C7443DD0-9344-40C4-874B-1767DBD50427}"/>
-    <hyperlink ref="A87" r:id="rId82" xr:uid="{AE4C65C3-8DCB-4AE5-8442-87A00ED8DCDB}"/>
-    <hyperlink ref="A88" r:id="rId83" xr:uid="{2CC71A87-9DD9-48D3-B3D0-197ABE68EDEE}"/>
-    <hyperlink ref="A89" r:id="rId84" xr:uid="{44AF49EA-475E-4A10-8D61-9C3C24AF667D}"/>
-    <hyperlink ref="A92" r:id="rId85" xr:uid="{1B9E0934-1E3E-44C6-ADF5-9D4FBE2966A9}"/>
-    <hyperlink ref="A93" r:id="rId86" xr:uid="{1512CE27-C7EE-4C2D-8EDC-C870908999A6}"/>
-    <hyperlink ref="A94" r:id="rId87" xr:uid="{4194F7AE-884A-4DC7-A28E-76CBEBD37199}"/>
-    <hyperlink ref="A91" r:id="rId88" xr:uid="{30AEC6DE-59B8-4F03-9BB0-94F9F7739D9A}"/>
-    <hyperlink ref="A55" r:id="rId89" xr:uid="{00567345-3DC5-4383-8379-17CFAA2A60F6}"/>
-    <hyperlink ref="A70" r:id="rId90" xr:uid="{23C81692-18EA-4785-AFF2-84B19A44313E}"/>
+    <hyperlink ref="A42" r:id="rId41" xr:uid="{526BBB12-7F38-4579-B263-6E7B821ED64B}"/>
+    <hyperlink ref="A43" r:id="rId42" xr:uid="{08991842-169D-4131-8E5C-0B23BF2231E4}"/>
+    <hyperlink ref="A44" r:id="rId43" xr:uid="{1980725C-6E8E-434A-BA30-7F025493AE0C}"/>
+    <hyperlink ref="A45" r:id="rId44" xr:uid="{A69D5B92-5F36-4F0D-8496-62C7779EF27C}"/>
+    <hyperlink ref="A46" r:id="rId45" xr:uid="{D58319EE-A17C-4704-B94D-03E499FA2F49}"/>
+    <hyperlink ref="A47" r:id="rId46" xr:uid="{920449F7-B769-4DA0-88C9-FC171552A0C2}"/>
+    <hyperlink ref="A49" r:id="rId47" xr:uid="{22DC2BD2-5ED5-453E-9772-4EBC80B76840}"/>
+    <hyperlink ref="A50" r:id="rId48" xr:uid="{B3016CBF-3B17-447C-8747-8883821F678C}"/>
+    <hyperlink ref="A51" r:id="rId49" xr:uid="{BCAD1D13-E879-487C-8991-BE4B5F26ED9D}"/>
+    <hyperlink ref="A52" r:id="rId50" xr:uid="{B24281AE-7CFB-4E77-8710-6C5C69DF0E3A}"/>
+    <hyperlink ref="A55" r:id="rId51" xr:uid="{9D345891-C64A-4116-9CBD-D8299A065AB2}"/>
+    <hyperlink ref="A56" r:id="rId52" xr:uid="{4A071EAE-97D2-4226-8320-18BD012FE980}"/>
+    <hyperlink ref="A57" r:id="rId53" xr:uid="{002D293B-E1E7-41D1-8F58-18CB033D4C0B}"/>
+    <hyperlink ref="A58" r:id="rId54" xr:uid="{CD479996-1364-46E4-8A92-9A6A42551FF6}"/>
+    <hyperlink ref="A59" r:id="rId55" xr:uid="{88C16AE5-2964-47DA-866E-C99E20C640BF}"/>
+    <hyperlink ref="A60" r:id="rId56" xr:uid="{DEE39071-BFD1-4659-BCBC-7253D2D83844}"/>
+    <hyperlink ref="A61" r:id="rId57" xr:uid="{124911A5-BF82-4A8A-90E3-3B307B75745A}"/>
+    <hyperlink ref="A62" r:id="rId58" xr:uid="{872676C7-BA93-44ED-8176-D65A522D055F}"/>
+    <hyperlink ref="A63" r:id="rId59" xr:uid="{8C69D9C5-F81F-43A4-88F1-F5072E510E74}"/>
+    <hyperlink ref="A64" r:id="rId60" xr:uid="{7AB8998F-8F34-45A4-B0AD-E6A7A0B2A881}"/>
+    <hyperlink ref="A65" r:id="rId61" xr:uid="{E59E2C03-FBE2-4EEE-AF2C-2EFBEABA12BE}"/>
+    <hyperlink ref="A66" r:id="rId62" xr:uid="{E98E434E-9191-4408-B92B-0C826578785E}"/>
+    <hyperlink ref="A67" r:id="rId63" xr:uid="{94690B43-F21E-4A61-B018-142AAE1B9ADB}"/>
+    <hyperlink ref="A70" r:id="rId64" xr:uid="{30179ED1-FF44-42C3-9D41-B7016703D894}"/>
+    <hyperlink ref="A71" r:id="rId65" xr:uid="{1ADF7731-1C78-48BE-AAA9-4C317A651BD8}"/>
+    <hyperlink ref="A72" r:id="rId66" xr:uid="{D2BC7663-6094-4414-9F29-42EB24D336C6}"/>
+    <hyperlink ref="A73" r:id="rId67" xr:uid="{2FFE24D8-5AB1-4F84-96BF-4128D22D12CC}"/>
+    <hyperlink ref="A74" r:id="rId68" xr:uid="{96A8D8B5-3A73-4548-814D-5DBC7029281A}"/>
+    <hyperlink ref="A53" r:id="rId69" xr:uid="{C95D41BC-2BE5-41DB-91BA-DDDADA812E67}"/>
+    <hyperlink ref="A75" r:id="rId70" xr:uid="{9C117DCB-567A-4238-B1DB-4E79F5FEFD0F}"/>
+    <hyperlink ref="A76" r:id="rId71" xr:uid="{39CDE5E9-80B4-431E-9B6A-23077E525A95}"/>
+    <hyperlink ref="A77" r:id="rId72" xr:uid="{851B6F22-EA97-4169-AFEA-1E55E7DAB8BB}"/>
+    <hyperlink ref="A78" r:id="rId73" xr:uid="{7211144F-07D8-4C74-998F-6DB44B3B9C9E}"/>
+    <hyperlink ref="A79" r:id="rId74" xr:uid="{269DB1EF-3835-4747-89A9-EF8F5B50AD58}"/>
+    <hyperlink ref="A80" r:id="rId75" xr:uid="{3A3D79C0-396E-45F0-9F95-323455383605}"/>
+    <hyperlink ref="A81" r:id="rId76" xr:uid="{7BD2167F-29F3-4974-8CCC-2A0B0452CDCB}"/>
+    <hyperlink ref="A82" r:id="rId77" xr:uid="{1E5B6BA8-A124-436E-B988-9A290CE1FF56}"/>
+    <hyperlink ref="A83" r:id="rId78" xr:uid="{8891F656-A5A3-4E45-B521-F203496DE824}"/>
+    <hyperlink ref="A84" r:id="rId79" xr:uid="{24F9B58E-0739-42CE-B33E-92641CD0D595}"/>
+    <hyperlink ref="A85" r:id="rId80" xr:uid="{C7443DD0-9344-40C4-874B-1767DBD50427}"/>
+    <hyperlink ref="A86" r:id="rId81" xr:uid="{AE4C65C3-8DCB-4AE5-8442-87A00ED8DCDB}"/>
+    <hyperlink ref="A87" r:id="rId82" xr:uid="{2CC71A87-9DD9-48D3-B3D0-197ABE68EDEE}"/>
+    <hyperlink ref="A88" r:id="rId83" xr:uid="{44AF49EA-475E-4A10-8D61-9C3C24AF667D}"/>
+    <hyperlink ref="A91" r:id="rId84" xr:uid="{1B9E0934-1E3E-44C6-ADF5-9D4FBE2966A9}"/>
+    <hyperlink ref="A92" r:id="rId85" xr:uid="{1512CE27-C7EE-4C2D-8EDC-C870908999A6}"/>
+    <hyperlink ref="A93" r:id="rId86" xr:uid="{4194F7AE-884A-4DC7-A28E-76CBEBD37199}"/>
+    <hyperlink ref="A90" r:id="rId87" xr:uid="{30AEC6DE-59B8-4F03-9BB0-94F9F7739D9A}"/>
+    <hyperlink ref="A54" r:id="rId88" xr:uid="{00567345-3DC5-4383-8379-17CFAA2A60F6}"/>
+    <hyperlink ref="A69" r:id="rId89" xr:uid="{23C81692-18EA-4785-AFF2-84B19A44313E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId91"/>
+  <pageSetup orientation="portrait" r:id="rId90"/>
 </worksheet>
 </file>
 

--- a/src/main/resources/AllCollectionPages.xlsx
+++ b/src/main/resources/AllCollectionPages.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vijeta\git\TJAutomation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vijeta\git\TJ_Automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC0805B-EA09-49AF-9F48-F0728FB9CBB4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{316D4C56-4ED8-4EAF-8FBB-5A9C4C7A1A9D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{6E36BB93-8918-4A7C-A9DF-2D6DC4D87C0E}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t>URLs</t>
   </si>
@@ -43,45 +43,12 @@
     <t>https://tommyjohn.com/collections/mens-new-arrivals-1</t>
   </si>
   <si>
-    <t>https://tommyjohn.com/collections/mens-gift-guide</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/limited-edition-gift-sets</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/toe-tally-cozy-holiday-socks</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/cotton-basic</t>
-  </si>
-  <si>
     <t>https://tommyjohn.com/collections/womens-new-arrivals</t>
   </si>
   <si>
-    <t>https://tommyjohn.com/collections/womens-holiday-gift-guide</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-limited-edition-holiday-gift-sets</t>
-  </si>
-  <si>
     <t>https://tommyjohn.com/collections/womens-socks</t>
   </si>
   <si>
-    <t>https://tommyjohn.com/collections/gifts-under-100</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/gifts-under-150</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/gifts-under-200</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/loungewear-1</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/mens-womens-underwear</t>
-  </si>
-  <si>
     <t>https://tommyjohn.com/collections/mens-underwear</t>
   </si>
   <si>
@@ -136,30 +103,18 @@
     <t>https://tommyjohn.com/collections/mens-socks</t>
   </si>
   <si>
-    <t>https://tommyjohn.com/collections/sock-packs-2</t>
-  </si>
-  <si>
     <t>https://tommyjohn.com/collections/all-clothing</t>
   </si>
   <si>
     <t>https://tommyjohn.com/collections/mens-tees-polos</t>
   </si>
   <si>
-    <t>https://tommyjohn.com/collections/stay-tucked-dress-shirts</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/mens-hoodies-jackets</t>
-  </si>
-  <si>
     <t>https://tommyjohn.com/collections/pants-and-shorts</t>
   </si>
   <si>
     <t>https://tommyjohn.com/collections/clothing-packs</t>
   </si>
   <si>
-    <t>https://tommyjohn.com/pages/mens-shop-the-look</t>
-  </si>
-  <si>
     <t>https://tommyjohn.com/collections/mens-second-skin</t>
   </si>
   <si>
@@ -193,9 +148,6 @@
     <t>https://tommyjohn.com/collections/womens-camisoles</t>
   </si>
   <si>
-    <t>http://tommyjohn.com/collections/womens-sleekheat</t>
-  </si>
-  <si>
     <t>https://tommyjohn.com/collections/bras</t>
   </si>
   <si>
@@ -220,9 +172,6 @@
     <t>https://tommyjohn.com/collections/womens-button-down-shirts</t>
   </si>
   <si>
-    <t>https://tommyjohn.com/collections/womens-hoodies-jackets</t>
-  </si>
-  <si>
     <t>https://tommyjohn.com/collections/womens-pants-shorts</t>
   </si>
   <si>
@@ -253,15 +202,9 @@
     <t>https://tommyjohn.com/collections/underwear-womens-styles-slip-shorts?style=Slip%20Shorts</t>
   </si>
   <si>
-    <t>https://tommyjohn.com/collections/mens-legging</t>
-  </si>
-  <si>
     <t>https://tommyjohn.com/collections/womens-slip-shorts</t>
   </si>
   <si>
-    <t>https://tommyjohn.com/pages/bras</t>
-  </si>
-  <si>
     <t>https://tommyjohn.com/collections/mens-pack</t>
   </si>
   <si>
@@ -271,9 +214,6 @@
     <t>https://tommyjohn.com/collections/mens-packs-section-tees</t>
   </si>
   <si>
-    <t>http://tommyjohn.com/collections/mens-lounge-packs</t>
-  </si>
-  <si>
     <t>https://tommyjohn.com/collections/sampler-packs-2</t>
   </si>
   <si>
@@ -292,28 +232,70 @@
     <t>https://tommyjohn.com/collections/womens-underwear-packs</t>
   </si>
   <si>
-    <t>https://tommyjohn.com/collections/womens-bralette-packs-section</t>
-  </si>
-  <si>
     <t>https://tommyjohn.com/collections/camisole-packs-1</t>
   </si>
   <si>
     <t>https://tommyjohn.com/collections/sampler-packs-1</t>
   </si>
   <si>
-    <t>https://tommyjohn.com/collections/tee-packs-2</t>
-  </si>
-  <si>
     <t>https://tommyjohn.com/collections/lounge-packs-1</t>
   </si>
   <si>
     <t>https://tommyjohn.com/collections/womens-sleepwear-sets-section</t>
   </si>
   <si>
-    <t>https://tommyjohn.com/pages/womens-shop-the-look</t>
-  </si>
-  <si>
     <t>https://tommyjohn.com/collections/womens-second-skin</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/over-the-calf-dress-socks</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/calf-socks</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/ankle-sock</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/no-show-sock</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/youth-socks-men-section</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/sweaters-sweatshirts-1</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/jackets-outerwear-1</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/kevin-harts-favorites</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/womens-underwear-packs-section</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/bra-womens-styles-lightly-lined-demi-bra?style=Lightly%20Lined%20Demi%20Bra</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/bra-womens-styles-lightly-lined-wireless-bra?style=Lightly%20Lined%20Wireless%20Bra</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/bra-womens-styles-scoop-bralette?style=Scoop%20Bralette</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/womens-second-skin-triangle-bralette</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/womens-hoodies-section-1</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/eniko-hart-favorites</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/mens-lounge-packs</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/all-mens-collections</t>
   </si>
 </sst>
 </file>
@@ -679,7 +661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2C82410-DE23-46B1-9D53-2AA20A124B74}">
-  <dimension ref="A1:A94"/>
+  <dimension ref="A1:A93"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="98.54296875" bestFit="1" customWidth="1"/>
@@ -691,562 +673,541 @@
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A46" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A47" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A48" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A52" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A53" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A55" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A56" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A57" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A58" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A59" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A23" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A26" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A28" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A29" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A30" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A31" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A32" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A33" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A34" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A35" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A36" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A37" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A38" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A39" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A40" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A41" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A42" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A43" s="1" t="s">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A60" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A44" s="1" t="s">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A61" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A45" s="1" t="s">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A62" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A46" s="1" t="s">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A63" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A64" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A47" s="1" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A65" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A48" s="1" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A66" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A49" s="1" t="s">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A67" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A50" s="1" t="s">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A68" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A51" s="1" t="s">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A69" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A52" s="1" t="s">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A70" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A53" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A54" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A55" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A56" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A57" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A58" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A59" s="1" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A71" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A72" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A60" s="1" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A73" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A61" s="1" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A74" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A62" s="1" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A75" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A76" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A77" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A63" s="1" t="s">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A78" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A64" s="1" t="s">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A79" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A65" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A66" s="1" t="s">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A80" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A67" s="1" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A81" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A82" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A68" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A69" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A70" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A71" s="1" t="s">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A83" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A84" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A85" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A72" s="1" t="s">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A86" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A73" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A74" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A75" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A76" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A77" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A78" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A79" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A80" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A81" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A82" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A83" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A84" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A85" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A86" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A87" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A88" s="1" t="s">
-        <v>85</v>
+      <c r="A87" s="2" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A89" s="1" t="s">
-        <v>90</v>
-      </c>
+      <c r="A89" s="1"/>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A90" s="1" t="s">
-        <v>89</v>
-      </c>
+      <c r="A90" s="1"/>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A91" s="1" t="s">
-        <v>86</v>
-      </c>
+      <c r="A91" s="1"/>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A92" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="A92" s="1"/>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A93" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A94" s="2"/>
+      <c r="A93" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{A2753353-4518-44AA-884F-E2ADBA84D480}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{08302394-8AB6-4E03-AF2A-03DA2C3F0D6D}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{7A64B147-2564-4C9C-9857-04D3A473F74E}"/>
-    <hyperlink ref="A5" r:id="rId4" xr:uid="{864A33F7-CC0E-45FF-839E-C13807357DD7}"/>
-    <hyperlink ref="A6" r:id="rId5" xr:uid="{2CC87552-8FE1-4701-91DC-F4042B50E4DD}"/>
-    <hyperlink ref="A7" r:id="rId6" xr:uid="{55607A89-71EB-4CE9-A54A-F28D6E7070DC}"/>
-    <hyperlink ref="A8" r:id="rId7" xr:uid="{0540F60D-8D98-460A-8052-D26CE99EF632}"/>
-    <hyperlink ref="A9" r:id="rId8" xr:uid="{D1CE5827-386A-47F7-9223-B8E05DEA39A3}"/>
-    <hyperlink ref="A10" r:id="rId9" xr:uid="{7FD380F2-F487-4C47-968A-61E7E1BB7589}"/>
-    <hyperlink ref="A11" r:id="rId10" xr:uid="{37506973-32DF-4968-8881-921C8EB0174E}"/>
-    <hyperlink ref="A12" r:id="rId11" xr:uid="{68CF95DC-B9C9-4939-868E-741AFFE8CFBF}"/>
-    <hyperlink ref="A13" r:id="rId12" xr:uid="{BB177064-29B6-45F8-AD78-B12E699A975B}"/>
-    <hyperlink ref="A14" r:id="rId13" xr:uid="{6BB9EB4B-9F33-425B-8EC6-73F4CAAD161C}"/>
-    <hyperlink ref="A15" r:id="rId14" xr:uid="{4838F18A-99B7-4DCD-B094-5AAF01F5A479}"/>
-    <hyperlink ref="A16" r:id="rId15" xr:uid="{5A74722A-2914-4BBE-9480-09A477753682}"/>
-    <hyperlink ref="A17" r:id="rId16" xr:uid="{4172B904-8DD0-42FD-930A-BDF332FCBF74}"/>
-    <hyperlink ref="A18" r:id="rId17" xr:uid="{875414B1-72E3-42B9-9CF8-04E61E66630F}"/>
-    <hyperlink ref="A19" r:id="rId18" xr:uid="{E4F3706E-FB12-4F6A-B251-04A97FB5C587}"/>
-    <hyperlink ref="A20" r:id="rId19" xr:uid="{E2D8B15B-312F-4685-8FCE-EE49893D6042}"/>
-    <hyperlink ref="A21" r:id="rId20" xr:uid="{4D2BE94A-6917-4EBF-AF3E-C9CB4DFC35B1}"/>
-    <hyperlink ref="A22" r:id="rId21" xr:uid="{81D79FC2-AACB-489D-B3B9-3E9F03E7E4B9}"/>
-    <hyperlink ref="A23" r:id="rId22" xr:uid="{7601DEEA-FE82-4A84-AA2F-3B8041A6B5D6}"/>
-    <hyperlink ref="A24" r:id="rId23" xr:uid="{6060BBD1-6E78-48F4-8020-A0F279B035D3}"/>
-    <hyperlink ref="A25" r:id="rId24" xr:uid="{2BEA64D2-EEB6-46E9-82B4-60567942D191}"/>
-    <hyperlink ref="A26" r:id="rId25" xr:uid="{A9F1B6C6-5B63-46CF-B5BB-84CCDF4B7E78}"/>
-    <hyperlink ref="A27" r:id="rId26" xr:uid="{1D8BEAAF-C383-4C66-A878-2E11124598A7}"/>
-    <hyperlink ref="A28" r:id="rId27" xr:uid="{C4FA394D-EC01-4328-B935-B8CFF3B4DC57}"/>
-    <hyperlink ref="A29" r:id="rId28" xr:uid="{77075B89-8471-461C-AF45-BA40D762DC82}"/>
-    <hyperlink ref="A30" r:id="rId29" xr:uid="{50274DFF-09A2-49A0-8A8A-4E0DA74AE921}"/>
-    <hyperlink ref="A31" r:id="rId30" xr:uid="{DD5025BB-D8B7-4248-A4B4-467F2E8EE5B9}"/>
-    <hyperlink ref="A32" r:id="rId31" xr:uid="{B8033B37-0B9B-4675-8157-EAAFAA37FD12}"/>
-    <hyperlink ref="A33" r:id="rId32" xr:uid="{0DB9801B-569A-4358-9C58-B742EADA4561}"/>
-    <hyperlink ref="A34" r:id="rId33" xr:uid="{7CFD71CD-0A4D-4D3A-BC38-CD569CF77776}"/>
-    <hyperlink ref="A35" r:id="rId34" xr:uid="{949C40C2-E922-4D2C-9111-242B051177A5}"/>
-    <hyperlink ref="A36" r:id="rId35" xr:uid="{316AC240-04D3-4BA8-B5A0-C5FECF53BD97}"/>
-    <hyperlink ref="A37" r:id="rId36" xr:uid="{048CC2B8-F9C0-4F38-8EE6-0D30C061F46C}"/>
-    <hyperlink ref="A38" r:id="rId37" xr:uid="{3B104A6D-EBF4-4CDB-885B-808A720D7E49}"/>
-    <hyperlink ref="A39" r:id="rId38" xr:uid="{DA49711C-4AFC-4B29-9915-ED2A27B3AF33}"/>
-    <hyperlink ref="A40" r:id="rId39" xr:uid="{F885B5BA-DBEB-44C4-919B-CC22C99E1B7D}"/>
-    <hyperlink ref="A41" r:id="rId40" xr:uid="{3720BD22-1543-40B5-ABF3-C3AFFB4C222C}"/>
-    <hyperlink ref="A42" r:id="rId41" xr:uid="{526BBB12-7F38-4579-B263-6E7B821ED64B}"/>
-    <hyperlink ref="A43" r:id="rId42" xr:uid="{08991842-169D-4131-8E5C-0B23BF2231E4}"/>
-    <hyperlink ref="A44" r:id="rId43" xr:uid="{1980725C-6E8E-434A-BA30-7F025493AE0C}"/>
-    <hyperlink ref="A45" r:id="rId44" xr:uid="{A69D5B92-5F36-4F0D-8496-62C7779EF27C}"/>
-    <hyperlink ref="A46" r:id="rId45" xr:uid="{D58319EE-A17C-4704-B94D-03E499FA2F49}"/>
-    <hyperlink ref="A47" r:id="rId46" xr:uid="{920449F7-B769-4DA0-88C9-FC171552A0C2}"/>
-    <hyperlink ref="A49" r:id="rId47" xr:uid="{22DC2BD2-5ED5-453E-9772-4EBC80B76840}"/>
-    <hyperlink ref="A50" r:id="rId48" xr:uid="{B3016CBF-3B17-447C-8747-8883821F678C}"/>
-    <hyperlink ref="A51" r:id="rId49" xr:uid="{BCAD1D13-E879-487C-8991-BE4B5F26ED9D}"/>
-    <hyperlink ref="A52" r:id="rId50" xr:uid="{B24281AE-7CFB-4E77-8710-6C5C69DF0E3A}"/>
-    <hyperlink ref="A55" r:id="rId51" xr:uid="{9D345891-C64A-4116-9CBD-D8299A065AB2}"/>
-    <hyperlink ref="A56" r:id="rId52" xr:uid="{4A071EAE-97D2-4226-8320-18BD012FE980}"/>
-    <hyperlink ref="A57" r:id="rId53" xr:uid="{002D293B-E1E7-41D1-8F58-18CB033D4C0B}"/>
-    <hyperlink ref="A58" r:id="rId54" xr:uid="{CD479996-1364-46E4-8A92-9A6A42551FF6}"/>
-    <hyperlink ref="A59" r:id="rId55" xr:uid="{88C16AE5-2964-47DA-866E-C99E20C640BF}"/>
-    <hyperlink ref="A60" r:id="rId56" xr:uid="{DEE39071-BFD1-4659-BCBC-7253D2D83844}"/>
-    <hyperlink ref="A61" r:id="rId57" xr:uid="{124911A5-BF82-4A8A-90E3-3B307B75745A}"/>
-    <hyperlink ref="A62" r:id="rId58" xr:uid="{872676C7-BA93-44ED-8176-D65A522D055F}"/>
-    <hyperlink ref="A63" r:id="rId59" xr:uid="{8C69D9C5-F81F-43A4-88F1-F5072E510E74}"/>
-    <hyperlink ref="A64" r:id="rId60" xr:uid="{7AB8998F-8F34-45A4-B0AD-E6A7A0B2A881}"/>
-    <hyperlink ref="A65" r:id="rId61" xr:uid="{E59E2C03-FBE2-4EEE-AF2C-2EFBEABA12BE}"/>
-    <hyperlink ref="A66" r:id="rId62" xr:uid="{E98E434E-9191-4408-B92B-0C826578785E}"/>
-    <hyperlink ref="A67" r:id="rId63" xr:uid="{94690B43-F21E-4A61-B018-142AAE1B9ADB}"/>
-    <hyperlink ref="A70" r:id="rId64" xr:uid="{30179ED1-FF44-42C3-9D41-B7016703D894}"/>
-    <hyperlink ref="A71" r:id="rId65" xr:uid="{1ADF7731-1C78-48BE-AAA9-4C317A651BD8}"/>
-    <hyperlink ref="A72" r:id="rId66" xr:uid="{D2BC7663-6094-4414-9F29-42EB24D336C6}"/>
-    <hyperlink ref="A73" r:id="rId67" xr:uid="{2FFE24D8-5AB1-4F84-96BF-4128D22D12CC}"/>
-    <hyperlink ref="A74" r:id="rId68" xr:uid="{96A8D8B5-3A73-4548-814D-5DBC7029281A}"/>
-    <hyperlink ref="A53" r:id="rId69" xr:uid="{C95D41BC-2BE5-41DB-91BA-DDDADA812E67}"/>
-    <hyperlink ref="A75" r:id="rId70" xr:uid="{9C117DCB-567A-4238-B1DB-4E79F5FEFD0F}"/>
-    <hyperlink ref="A76" r:id="rId71" xr:uid="{39CDE5E9-80B4-431E-9B6A-23077E525A95}"/>
-    <hyperlink ref="A77" r:id="rId72" xr:uid="{851B6F22-EA97-4169-AFEA-1E55E7DAB8BB}"/>
-    <hyperlink ref="A78" r:id="rId73" xr:uid="{7211144F-07D8-4C74-998F-6DB44B3B9C9E}"/>
-    <hyperlink ref="A79" r:id="rId74" xr:uid="{269DB1EF-3835-4747-89A9-EF8F5B50AD58}"/>
-    <hyperlink ref="A80" r:id="rId75" xr:uid="{3A3D79C0-396E-45F0-9F95-323455383605}"/>
-    <hyperlink ref="A81" r:id="rId76" xr:uid="{7BD2167F-29F3-4974-8CCC-2A0B0452CDCB}"/>
-    <hyperlink ref="A82" r:id="rId77" xr:uid="{1E5B6BA8-A124-436E-B988-9A290CE1FF56}"/>
-    <hyperlink ref="A83" r:id="rId78" xr:uid="{8891F656-A5A3-4E45-B521-F203496DE824}"/>
-    <hyperlink ref="A84" r:id="rId79" xr:uid="{24F9B58E-0739-42CE-B33E-92641CD0D595}"/>
-    <hyperlink ref="A85" r:id="rId80" xr:uid="{C7443DD0-9344-40C4-874B-1767DBD50427}"/>
-    <hyperlink ref="A86" r:id="rId81" xr:uid="{AE4C65C3-8DCB-4AE5-8442-87A00ED8DCDB}"/>
-    <hyperlink ref="A87" r:id="rId82" xr:uid="{2CC71A87-9DD9-48D3-B3D0-197ABE68EDEE}"/>
-    <hyperlink ref="A88" r:id="rId83" xr:uid="{44AF49EA-475E-4A10-8D61-9C3C24AF667D}"/>
-    <hyperlink ref="A91" r:id="rId84" xr:uid="{1B9E0934-1E3E-44C6-ADF5-9D4FBE2966A9}"/>
-    <hyperlink ref="A92" r:id="rId85" xr:uid="{1512CE27-C7EE-4C2D-8EDC-C870908999A6}"/>
-    <hyperlink ref="A93" r:id="rId86" xr:uid="{4194F7AE-884A-4DC7-A28E-76CBEBD37199}"/>
-    <hyperlink ref="A90" r:id="rId87" xr:uid="{30AEC6DE-59B8-4F03-9BB0-94F9F7739D9A}"/>
-    <hyperlink ref="A54" r:id="rId88" xr:uid="{00567345-3DC5-4383-8379-17CFAA2A60F6}"/>
-    <hyperlink ref="A69" r:id="rId89" xr:uid="{23C81692-18EA-4785-AFF2-84B19A44313E}"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{A482861F-8E7B-4046-8382-4F8E33A49FD7}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{04BF0EE6-5DE9-4C3E-8D53-8E463F08745F}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{B2D37466-5BE3-4EA5-B825-D999FCCD4363}"/>
+    <hyperlink ref="A5" r:id="rId4" xr:uid="{723282CB-5EE7-4286-A9A6-B7B35954809C}"/>
+    <hyperlink ref="A6" r:id="rId5" xr:uid="{818F5EC8-414C-43D4-9B36-E66E07CAFBAC}"/>
+    <hyperlink ref="A7" r:id="rId6" xr:uid="{B5EBF533-1AE1-4364-B4CA-1001C237D820}"/>
+    <hyperlink ref="A8" r:id="rId7" xr:uid="{8C72FF69-25B6-4C52-9D12-0470DD16B01A}"/>
+    <hyperlink ref="A9" r:id="rId8" xr:uid="{B6110CD2-78DE-47C6-B175-98E0250A4964}"/>
+    <hyperlink ref="A10" r:id="rId9" xr:uid="{4327837E-3057-49DD-891C-491A479165DF}"/>
+    <hyperlink ref="A11" r:id="rId10" xr:uid="{3822D4A6-CE4A-4D67-B2EE-1C2016F7B61F}"/>
+    <hyperlink ref="A12" r:id="rId11" xr:uid="{1FA70101-95F4-4080-96C2-CC2003270A3E}"/>
+    <hyperlink ref="A13" r:id="rId12" xr:uid="{FA168982-CF0E-4A52-8978-7A6D1964C685}"/>
+    <hyperlink ref="A14" r:id="rId13" xr:uid="{82BBC9DC-5A89-4C9C-ADBB-37CCC481FFD7}"/>
+    <hyperlink ref="A15" r:id="rId14" xr:uid="{1629CAAC-9FEB-4D94-9AFD-B186AB751A10}"/>
+    <hyperlink ref="A16" r:id="rId15" xr:uid="{428BE50C-7110-4869-A6C2-3027481126E4}"/>
+    <hyperlink ref="A17" r:id="rId16" xr:uid="{62A93C0A-3548-43F7-BCEC-C2A6E548EF74}"/>
+    <hyperlink ref="A18" r:id="rId17" xr:uid="{C38A4AE2-D2E6-49FC-B4AF-DD7C46D7AF60}"/>
+    <hyperlink ref="A19" r:id="rId18" xr:uid="{D0E54FB1-8086-47E8-AB8D-47AF4CAB5EC7}"/>
+    <hyperlink ref="A20" r:id="rId19" xr:uid="{2104E24D-45E9-4DF3-9E48-BEB10B754EC8}"/>
+    <hyperlink ref="A21" r:id="rId20" xr:uid="{64DE9C8D-B68E-4158-9BE2-F4879F14F8E5}"/>
+    <hyperlink ref="A22" r:id="rId21" xr:uid="{653DD843-E1C9-43C5-8544-B39C9F38C2B9}"/>
+    <hyperlink ref="A23" r:id="rId22" xr:uid="{0629C03E-A665-4ADA-B099-2B92415C9F40}"/>
+    <hyperlink ref="A24" r:id="rId23" xr:uid="{5E86BFA9-4B9F-4E76-A31E-51863291D45B}"/>
+    <hyperlink ref="A25" r:id="rId24" xr:uid="{ACD3A4C3-A393-4007-870F-965A6816C30F}"/>
+    <hyperlink ref="A26" r:id="rId25" xr:uid="{8B54BCF6-512E-4AED-90DB-51198C93F9AE}"/>
+    <hyperlink ref="A27" r:id="rId26" xr:uid="{C6B61FA5-2399-4AA0-B784-77A38B2CEF5B}"/>
+    <hyperlink ref="A28" r:id="rId27" xr:uid="{AF795EC0-403F-4C9D-A613-BB11BDFC2146}"/>
+    <hyperlink ref="A31" r:id="rId28" xr:uid="{317E087E-D266-4500-8FB9-49550CE6FBA7}"/>
+    <hyperlink ref="A32" r:id="rId29" xr:uid="{41E20D85-9D83-4F0B-81A6-44FB31A19C07}"/>
+    <hyperlink ref="A87" r:id="rId30" xr:uid="{35D1EC71-390F-45DC-AB14-060F6B19BFA7}"/>
+    <hyperlink ref="A33" r:id="rId31" xr:uid="{1103231E-5DE4-40FD-A75C-3CFF021D8284}"/>
+    <hyperlink ref="A34" r:id="rId32" xr:uid="{0D58ED00-CB6C-40F9-A2C0-58C2FF7C70F1}"/>
+    <hyperlink ref="A35" r:id="rId33" xr:uid="{269898E8-24BA-4C65-8189-85CE60F8A51F}"/>
+    <hyperlink ref="A36" r:id="rId34" xr:uid="{8D7EC1CF-7159-4CDF-8CE7-C8C3EE770739}"/>
+    <hyperlink ref="A37" r:id="rId35" xr:uid="{B4EB66A7-D6FE-4A81-98D7-64DE071BB3DD}"/>
+    <hyperlink ref="A38" r:id="rId36" xr:uid="{CA7B25AA-F635-48F8-9672-44D27C5E4539}"/>
+    <hyperlink ref="A39" r:id="rId37" xr:uid="{899CB714-6AF5-45F1-9DEA-B52C384CCFDC}"/>
+    <hyperlink ref="A40" r:id="rId38" xr:uid="{141ECD87-6002-4B9B-9C19-73F3A073239F}"/>
+    <hyperlink ref="A41" r:id="rId39" xr:uid="{6A2C576B-EC8F-4BC5-8D38-A235A47B2E8F}"/>
+    <hyperlink ref="A42" r:id="rId40" xr:uid="{08B65C9C-6B15-473C-B2E1-26D5D7875E3D}"/>
+    <hyperlink ref="A43" r:id="rId41" xr:uid="{60B35225-503D-4167-ACC6-2DA4315D5637}"/>
+    <hyperlink ref="A44" r:id="rId42" xr:uid="{E35A004F-B4C3-49BA-94E7-971978578840}"/>
+    <hyperlink ref="A45" r:id="rId43" xr:uid="{B87C5154-49F7-4A3E-A1C9-4EE76B032881}"/>
+    <hyperlink ref="A46" r:id="rId44" xr:uid="{30A11725-4F1C-4557-A7FF-DEA7C18269C7}"/>
+    <hyperlink ref="A47" r:id="rId45" xr:uid="{BC61C460-D4B5-46DD-948E-A3C128A14225}"/>
+    <hyperlink ref="A48" r:id="rId46" xr:uid="{486EC8B7-B56F-48A4-BF79-D789D79C9180}"/>
+    <hyperlink ref="A50" r:id="rId47" xr:uid="{AC315320-7D97-487B-8421-F033E9AFED6E}"/>
+    <hyperlink ref="A55" r:id="rId48" xr:uid="{F33CB65A-7191-41D5-9324-CEC998349FB5}"/>
+    <hyperlink ref="A56" r:id="rId49" xr:uid="{759CDA57-F14A-40D6-8368-5ABF96D65E13}"/>
+    <hyperlink ref="A57" r:id="rId50" xr:uid="{523CCC96-2127-4CCF-B5C1-6CE976176750}"/>
+    <hyperlink ref="A58" r:id="rId51" xr:uid="{EAD53362-445E-402C-AC5D-925FD73C7BCB}"/>
+    <hyperlink ref="A59" r:id="rId52" xr:uid="{529BAA6E-1C12-45E7-9A98-668AAD755221}"/>
+    <hyperlink ref="A60" r:id="rId53" xr:uid="{0E9D0576-772F-45A4-800C-995E8D4D50DE}"/>
+    <hyperlink ref="A61" r:id="rId54" xr:uid="{31E51FC8-B795-4C2A-A60D-226C26759A1F}"/>
+    <hyperlink ref="A62" r:id="rId55" xr:uid="{0F2C5E05-3A03-4308-A758-1692EDD95FB8}"/>
+    <hyperlink ref="A64" r:id="rId56" xr:uid="{A0571E97-7B8F-40AB-B43E-C2BF3954206F}"/>
+    <hyperlink ref="A65" r:id="rId57" xr:uid="{8193BCC5-F3BC-430E-B15E-A5F3F57F61F7}"/>
+    <hyperlink ref="A66" r:id="rId58" xr:uid="{6F8A86C8-2A08-470D-AA15-D5807CF523A1}"/>
+    <hyperlink ref="A67" r:id="rId59" xr:uid="{E5C1D8C7-DA31-475E-B28A-D3BF7FB7A0C4}"/>
+    <hyperlink ref="A68" r:id="rId60" xr:uid="{54683F35-8B73-44F4-BBE9-F63C1CD1D7E3}"/>
+    <hyperlink ref="A69" r:id="rId61" xr:uid="{35F5B87F-9C39-478B-9563-8E581C71825A}"/>
+    <hyperlink ref="A71" r:id="rId62" xr:uid="{844B6A05-0F69-438A-A12C-25D5A35C7B5A}"/>
+    <hyperlink ref="A70" r:id="rId63" xr:uid="{64565E9D-7C3B-4951-B91B-944A1F462533}"/>
+    <hyperlink ref="A72" r:id="rId64" xr:uid="{7D29E84B-A150-458F-8E38-4FC2A461E0A1}"/>
+    <hyperlink ref="A73" r:id="rId65" xr:uid="{5C531A56-00A3-4096-9CFD-4837D1D46C4F}"/>
+    <hyperlink ref="A74" r:id="rId66" xr:uid="{261FEB48-1252-42F6-BB71-AFE0E386A4ED}"/>
+    <hyperlink ref="A75" r:id="rId67" xr:uid="{E895938D-6FA5-40ED-A49F-E45881DF4325}"/>
+    <hyperlink ref="A77" r:id="rId68" xr:uid="{64E85A32-F4AE-4F99-94B8-44E7A063E089}"/>
+    <hyperlink ref="A78" r:id="rId69" xr:uid="{EDA4BC0E-3284-48CA-B6A9-CC80084C6187}"/>
+    <hyperlink ref="A79" r:id="rId70" xr:uid="{87A3F6F4-BDE6-4891-BEA0-7A5CB022698B}"/>
+    <hyperlink ref="A80" r:id="rId71" xr:uid="{C983F661-5E5B-4006-9566-847E5AE788EB}"/>
+    <hyperlink ref="A81" r:id="rId72" xr:uid="{58CF9B5D-2848-4A29-8340-4751211B724E}"/>
+    <hyperlink ref="A82" r:id="rId73" xr:uid="{11A476D9-ED9E-4CF0-970C-CE1375DC998D}"/>
+    <hyperlink ref="A83" r:id="rId74" xr:uid="{A987DDE2-EE85-43C7-9D8A-74DDABA95737}"/>
+    <hyperlink ref="A84" r:id="rId75" xr:uid="{0283D9C3-8FB9-4720-9341-BF9701B67F75}"/>
+    <hyperlink ref="A85" r:id="rId76" xr:uid="{86E53F0D-5609-4DF8-A81C-64130BCAB42F}"/>
+    <hyperlink ref="A86" r:id="rId77" xr:uid="{54107A10-0931-4E70-A9D8-63F496AC8831}"/>
+    <hyperlink ref="A29" r:id="rId78" xr:uid="{8D68FB9D-ACBD-4984-A549-2DC9A283862C}"/>
+    <hyperlink ref="A30" r:id="rId79" xr:uid="{6BC49A12-3C49-47FC-B870-7AA2BDB72BB4}"/>
+    <hyperlink ref="A49" r:id="rId80" xr:uid="{AA8123D1-3127-4629-8AE3-687AEA7A32F9}"/>
+    <hyperlink ref="A51" r:id="rId81" xr:uid="{95874106-3521-4497-ADC4-660C3DB53E72}"/>
+    <hyperlink ref="A52" r:id="rId82" xr:uid="{BEBC2E8F-8852-4A54-980C-3AB2C6F70350}"/>
+    <hyperlink ref="A53" r:id="rId83" xr:uid="{D4503CE2-9DA1-4CC3-8222-B958921D2F19}"/>
+    <hyperlink ref="A54" r:id="rId84" xr:uid="{7415671B-6FDA-43EF-BD84-0C2B6A0315E2}"/>
+    <hyperlink ref="A63" r:id="rId85" xr:uid="{D310A1CA-136D-46BE-B065-397034F95205}"/>
+    <hyperlink ref="A76" r:id="rId86" xr:uid="{D285BB45-E2AD-4CEC-BE46-C12A42A90798}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId90"/>
+  <pageSetup orientation="portrait" r:id="rId87"/>
 </worksheet>
 </file>
 

--- a/src/main/resources/AllCollectionPages.xlsx
+++ b/src/main/resources/AllCollectionPages.xlsx
@@ -1,24 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vijeta\git\TJ_Automation\src\main\resources\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C61F45-516B-4849-AC79-1CC114C3CBDD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{6E36BB93-8918-4A7C-A9DF-2D6DC4D87C0E}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15210" windowHeight="4995"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$61</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
   <si>
     <t>https://tommyjohn.com/collections/mens-new-arrivals-1</t>
   </si>
@@ -132,208 +127,277 @@
     <t>https://tommyjohn.com/collections/jackets-outerwear-1</t>
   </si>
   <si>
+    <t>https://tommyjohn.com/collections/all-womens</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/sale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://tommyjohn.com/collections/mens-underwear </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://tommyjohn.com/collections/mens-undershirts </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://tommyjohn.com/collections/loungewear </t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/mens-sale</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/new-arrivals-mens-underwear</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/new-arrivals-mens-lounge-sleep</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/new-arrivals-mens-packs</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/new-arrivals-clothing</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/bestsellers-2</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/underwear-mens-styles-boxer-brief</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/underwear-mens-styles-trunk</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/underwear-mens-styles-relaxed-fit-boxer-short</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/underwear-mens-styles-square-cut</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/underwear-mens-styles-brief</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/underwear-mens-styles-mid-length-boxer-brief</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/mens-legging</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/mens-crew-neck-undershirts</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/mens-high-v-neck-undershirts</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/mens-deep-v-neck-undershirts</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/mens-tanks</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/loungewear-2</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/mens-lounge-sleep-tops</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/mens-sale-tees-polos</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/mens-sale-undershirts</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/mens-sale-sweaters-jackets</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/mens-sale-button-downs</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/mens-sale-socks</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/mens-sale-underwear</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/mens-sale-lounge-sleep</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/mens-sale-clothing</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/mens-shirts</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/kevin-hart</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/new-arrivals-womens-lounge-sleep</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/new-arrivals-womens-packs</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/comfort-smoothing-plp</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/new-arrivals-womens-clothing</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/womens-bestsellers</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/bra-womens-styles-triangle-bralette</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/bra-womens-styles-lightly-lined-demi-bra</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/bra-womens-styles-lightly-lined-wireless-bra</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/bra-womens-styles-scoop-bralette</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/underwear-womens-styles-brief</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/underwear-womens-styles-cheeky</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/womens-high-rise-brief</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/underwear-womens-styles-thong</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/underwear-womens-styles-boyshort</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/underwear-womens-styles-slip-shorts</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/womens-lounge-sleep-bottoms</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/womens-lounge-sleep-tops</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/womens-lounge-sleep-packs</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/womens-sale-underwear</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/womens-sale-lounge-sleep</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/womens-sale-tops-tees</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/womens-sale-joggers</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/womens-sale-sweaters-jackets</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/womens-sale-camisoles</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/womens-sale-clothing</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/womens-tops-tees</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/womens-sweatshirts-jackets</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/womens-dresses</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/womens-all-socks</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/mens-sale-pants-joggers</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/womens-sale</t>
+  </si>
+  <si>
     <t>https://tommyjohn.com/collections/mens</t>
   </si>
   <si>
-    <t>https://tommyjohn.com/collections/all-womens</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/sale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://tommyjohn.com/collections/mens-underwear </t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://tommyjohn.com/collections/mens-undershirts </t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://tommyjohn.com/collections/loungewear </t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/mens-sale</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/new-arrivals-mens-underwear</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/new-arrivals-mens-lounge-sleep</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/new-arrivals-mens-packs</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/new-arrivals-clothing</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/bestsellers-2</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/underwear-mens-styles-boxer-brief</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/underwear-mens-styles-trunk</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/underwear-mens-styles-relaxed-fit-boxer-short</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/underwear-mens-styles-square-cut</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/underwear-mens-styles-brief</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/underwear-mens-styles-mid-length-boxer-brief</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/mens-legging</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/mens-crew-neck-undershirts</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/mens-high-v-neck-undershirts</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/mens-deep-v-neck-undershirts</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/mens-tanks</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/loungewear-2</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/mens-lounge-sleep-tops</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/mens-sale-tees-polos</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/mens-sale-undershirts</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/mens-sale-sweaters-jackets</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/mens-sale-button-downs</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/mens-sale-socks</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/mens-sale-underwear</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/mens-sale-lounge-sleep</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/mens-sale-clothing</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/mens-shirts</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/kevin-hart</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/new-arrivals-womens-lounge-sleep</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/new-arrivals-womens-packs</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/comfort-smoothing-plp</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/new-arrivals-womens-clothing</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-bestsellers</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/bra-womens-styles-triangle-bralette</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/bra-womens-styles-lightly-lined-demi-bra</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/bra-womens-styles-lightly-lined-wireless-bra</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/bra-womens-styles-scoop-bralette</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/underwear-womens-styles-brief</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/underwear-womens-styles-cheeky</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-high-rise-brief</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/underwear-womens-styles-thong</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/underwear-womens-styles-boyshort</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/underwear-womens-styles-slip-shorts</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-lounge-sleep-bottoms</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-lounge-sleep-tops</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-lounge-sleep-packs</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-sale-underwear</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-sale-lounge-sleep</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-sale-tops-tees</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-sale-joggers</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-sale-sweaters-jackets</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-sale-camisoles</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-sale-clothing</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-tops-tees</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-sweatshirts-jackets</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-dresses</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-all-socks</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/mens-sale-pants-joggers</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-sale</t>
+    <t>https://tommyjohn.com/collections/gift-cards</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/gift-guide-men</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/gift-guide-women</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/gift-guide-dual-gender</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/new-arrivals-mens</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/loungewear-mens</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/mens-lounge-pajama-bottoms</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/mens-lounge-pajama-tops</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/pajamas-mens</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/mens-lounge-sleep-packs</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/womens-lace</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/loungewear-womens</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/womens-lounge-bottoms</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/womens-lounge-tops</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/pajamas-womens</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/bralette-packs</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/womens-work-from-home</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/womens-work-from-home-loungewear</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/womens-work-from-home-underwear</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/womens-work-from-home-clothing</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/gifts-under-25-all</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/gifts-under-50-all</t>
+  </si>
+  <si>
+    <t>https://tommyjohn.com/collections/gifts-under-75-all</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -692,519 +756,636 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0A92C8C-C1EC-48C2-A6C1-E0CB36E8F620}">
-  <dimension ref="A1:A100"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A123"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="98.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="98.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
-        <v>99</v>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A5" r:id="rId1" xr:uid="{385FE0DC-4F6A-42B9-9489-D356AAFDA844}"/>
-    <hyperlink ref="A6" r:id="rId2" xr:uid="{D97B000E-FE03-442D-96C0-2BCFE8ADD00B}"/>
-    <hyperlink ref="A7" r:id="rId3" xr:uid="{49C47410-F70F-40E2-BA19-B128F4D9BE96}"/>
-    <hyperlink ref="A9" r:id="rId4" xr:uid="{EF6852F8-BBC3-4124-B5B4-822962DAE39B}"/>
+    <hyperlink ref="A9" r:id="rId1"/>
+    <hyperlink ref="A10" r:id="rId2"/>
+    <hyperlink ref="A11" r:id="rId3"/>
+    <hyperlink ref="A13" r:id="rId4"/>
+    <hyperlink ref="A1" r:id="rId5"/>
+    <hyperlink ref="A17" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/AllCollectionPages.xlsx
+++ b/src/main/resources/AllCollectionPages.xlsx
@@ -1,19 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23901"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vijeta\git\TJ_Automation\src\main\resources\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D47F69B-B8AA-48C7-B973-A8C18FCD3F65}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15210" windowHeight="4995"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$A$62</definedName>
   </definedNames>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -23,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
   <si>
     <t>https://tommyjohn.com/collections/mens-new-arrivals-1</t>
   </si>
@@ -46,12 +51,6 @@
     <t>https://tommyjohn.com/collections/all-clothing</t>
   </si>
   <si>
-    <t>https://tommyjohn.com/collections/mens-tees-polos</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/pants-and-shorts</t>
-  </si>
-  <si>
     <t>https://tommyjohn.com/collections/clothing-packs</t>
   </si>
   <si>
@@ -121,18 +120,9 @@
     <t>https://tommyjohn.com/collections/youth-socks-men-section</t>
   </si>
   <si>
-    <t>https://tommyjohn.com/collections/sweaters-sweatshirts-1</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/jackets-outerwear-1</t>
-  </si>
-  <si>
     <t>https://tommyjohn.com/collections/all-womens</t>
   </si>
   <si>
-    <t>https://tommyjohn.com/collections/sale</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://tommyjohn.com/collections/mens-underwear </t>
   </si>
   <si>
@@ -142,9 +132,6 @@
     <t xml:space="preserve">https://tommyjohn.com/collections/loungewear </t>
   </si>
   <si>
-    <t>https://tommyjohn.com/collections/mens-sale</t>
-  </si>
-  <si>
     <t>https://tommyjohn.com/collections/new-arrivals-mens-underwear</t>
   </si>
   <si>
@@ -199,30 +186,6 @@
     <t>https://tommyjohn.com/collections/mens-lounge-sleep-tops</t>
   </si>
   <si>
-    <t>https://tommyjohn.com/collections/mens-sale-tees-polos</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/mens-sale-undershirts</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/mens-sale-sweaters-jackets</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/mens-sale-button-downs</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/mens-sale-socks</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/mens-sale-underwear</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/mens-sale-lounge-sleep</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/mens-sale-clothing</t>
-  </si>
-  <si>
     <t>https://tommyjohn.com/collections/mens-shirts</t>
   </si>
   <si>
@@ -328,15 +291,6 @@
     <t>https://tommyjohn.com/collections/gift-cards</t>
   </si>
   <si>
-    <t>https://tommyjohn.com/collections/gift-guide-men</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/gift-guide-women</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/gift-guide-dual-gender</t>
-  </si>
-  <si>
     <t>https://tommyjohn.com/collections/new-arrivals-mens</t>
   </si>
   <si>
@@ -361,43 +315,19 @@
     <t>https://tommyjohn.com/collections/loungewear-womens</t>
   </si>
   <si>
-    <t>https://tommyjohn.com/collections/womens-lounge-bottoms</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-lounge-tops</t>
-  </si>
-  <si>
     <t>https://tommyjohn.com/collections/pajamas-womens</t>
   </si>
   <si>
     <t>https://tommyjohn.com/collections/bralette-packs</t>
   </si>
   <si>
-    <t>https://tommyjohn.com/collections/womens-work-from-home</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-work-from-home-loungewear</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-work-from-home-underwear</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-work-from-home-clothing</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/gifts-under-25-all</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/gifts-under-50-all</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/gifts-under-75-all</t>
+    <t>URLs</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -756,636 +686,512 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A123"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:A98"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="98.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="98.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>122</v>
-      </c>
-    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A9" r:id="rId1"/>
-    <hyperlink ref="A10" r:id="rId2"/>
-    <hyperlink ref="A11" r:id="rId3"/>
-    <hyperlink ref="A13" r:id="rId4"/>
-    <hyperlink ref="A1" r:id="rId5"/>
-    <hyperlink ref="A17" r:id="rId6"/>
+    <hyperlink ref="A6" r:id="rId1" xr:uid="{98E17712-DE89-4F4D-8F98-F76F0031EF2F}"/>
+    <hyperlink ref="A7" r:id="rId2" xr:uid="{D2385662-B314-419A-B5D8-DF106799304E}"/>
+    <hyperlink ref="A8" r:id="rId3" xr:uid="{EEC52897-73DB-4F3B-9403-F15653D735D6}"/>
+    <hyperlink ref="A9" r:id="rId4" xr:uid="{96131781-1525-418D-85AB-FB1F70170CED}"/>
+    <hyperlink ref="A2" r:id="rId5" xr:uid="{CE4AEB79-F9AE-4730-BBED-8C26BF5D373C}"/>
+    <hyperlink ref="A13" r:id="rId6" xr:uid="{68E912E9-931C-4769-8998-8823509BE697}"/>
+    <hyperlink ref="A3" r:id="rId7" xr:uid="{42E071B9-30D8-4750-B517-BB6DCB7412DE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/AllCollectionPages.xlsx
+++ b/src/main/resources/AllCollectionPages.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vijeta\git\TJ_Automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D47F69B-B8AA-48C7-B973-A8C18FCD3F65}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7834F67-AECB-4F68-925F-B4E45A31BB0F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
   <si>
     <t>https://tommyjohn.com/collections/mens-new-arrivals-1</t>
   </si>
@@ -246,27 +246,6 @@
     <t>https://tommyjohn.com/collections/womens-lounge-sleep-packs</t>
   </si>
   <si>
-    <t>https://tommyjohn.com/collections/womens-sale-underwear</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-sale-lounge-sleep</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-sale-tops-tees</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-sale-joggers</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-sale-sweaters-jackets</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-sale-camisoles</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/womens-sale-clothing</t>
-  </si>
-  <si>
     <t>https://tommyjohn.com/collections/womens-tops-tees</t>
   </si>
   <si>
@@ -277,9 +256,6 @@
   </si>
   <si>
     <t>https://tommyjohn.com/collections/womens-all-socks</t>
-  </si>
-  <si>
-    <t>https://tommyjohn.com/collections/mens-sale-pants-joggers</t>
   </si>
   <si>
     <t>https://tommyjohn.com/collections/womens-sale</t>
@@ -687,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A98"/>
+  <dimension ref="A1:A90"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="98.54296875" bestFit="1" customWidth="1"/>
@@ -695,12 +671,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
@@ -710,7 +686,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
@@ -1035,152 +1011,112 @@
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>72</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>74</v>
+        <v>17</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>19</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>88</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>
